--- a/gcomp/demo/demo_gcomptab.xlsx
+++ b/gcomp/demo/demo_gcomptab.xlsx
@@ -6,20 +6,111 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Normal CI" sheetId="1" r:id="rId2"/>
-    <sheet name="Percentile CI" sheetId="2" r:id="rId4"/>
+    <sheet name="Component models" sheetId="1" r:id="rId2"/>
+    <sheet name="Normal CI" sheetId="2" r:id="rId4"/>
+    <sheet name="Percentile CI" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="70" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="148" uniqueCount="61">
   <si>
-    <t>Table 1. Causal Mediation Analysis (Normal CIs)</t>
+    <t>Table 3. Fitted component models (odds ratios)</t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>Mediator (m)</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>95% CI</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>Outcome (y)</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>1.627***</t>
+  </si>
+  <si>
+    <t>[1.226, 2.160]</t>
+  </si>
+  <si>
+    <t>&lt;0.001</t>
+  </si>
+  <si>
+    <t>1.251</t>
+  </si>
+  <si>
+    <t>[0.873, 1.792]</t>
+  </si>
+  <si>
+    <t>0.223</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>1.009</t>
+  </si>
+  <si>
+    <t>[0.996, 1.021]</t>
+  </si>
+  <si>
+    <t>0.180</t>
+  </si>
+  <si>
+    <t>1.028***</t>
+  </si>
+  <si>
+    <t>[1.012, 1.045]</t>
+  </si>
+  <si>
+    <t>_cons</t>
+  </si>
+  <si>
+    <t>0.420**</t>
+  </si>
+  <si>
+    <t>[0.222, 0.795]</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>0.036***</t>
+  </si>
+  <si>
+    <t>[0.015, 0.087]</t>
+  </si>
+  <si>
+    <t>m</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>1.803***</t>
+  </si>
+  <si>
+    <t>[1.292, 2.516]</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Table 1. Causal Mediation Analysis (Normal CIs)</t>
   </si>
   <si>
     <t>Effect</t>
@@ -56,9 +147,6 @@
   </si>
   <si>
     <t>-0.016</t>
-  </si>
-  <si>
-    <t>95% CI</t>
   </si>
   <si>
     <t>(-0.047, 0.075)</t>
@@ -116,10 +204,797 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="273">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="639">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <i/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <i/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1242,6 +2117,793 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <i/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <i/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1256,13 +2918,874 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="195">
+  <borders count="441">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
     </border>
     <border/>
     <border/>
@@ -2550,750 +5073,2595 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="441">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0"/>
+    <xf numFmtId="0" fontId="185" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="187" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="189" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="191" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="193" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="195" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="197" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="203" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="207" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="247" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="266" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="268" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" xfId="0"/>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="188" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="190" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="192" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="194" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="196" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="198" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="200" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="202" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="204" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="206" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="208" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="210" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="212" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="214" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="216" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="217" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="270" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="287" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="289" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="291" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="293" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="299" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="301" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="305" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="307" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="309" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="313" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="315" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="317" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="319" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="221" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="225" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="226" xfId="0"/>
+    <xf numFmtId="0" fontId="321" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="323" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="325" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="329" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="331" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="333" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="335" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="337" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="339" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="341" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="343" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="347" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="349" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="351" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="353" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="357" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="359" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="361" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="367" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="369" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="371" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="373" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="375" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="377" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="379" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="381" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="383" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="385" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="387" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="389" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="391" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="397" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="399" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="218" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="401" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="219" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="221" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="404" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="223" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="225" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="227" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="229" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="230" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="231" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="232" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="233" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="234" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="235" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="236" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="237" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="238" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="239" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="240" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="241" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="242" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="243" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="244" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="245" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="246" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="247" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="248" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="249" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="250" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="251" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="252" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="253" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="254" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="255" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="256" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="257" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="258" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="259" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="260" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="261" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="262" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="263" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="264" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="265" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="266" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="267" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="268" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="269" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="270" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="271" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="272" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="406" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="412" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="414" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="416" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="418" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="420" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="422" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="438" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="439" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="481" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="491" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="493" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="499" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="501" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="502" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="503" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="505" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="507" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="508" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="509" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="511" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="513" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="515" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="517" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="519" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="521" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="523" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="525" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="527" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="529" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="530" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="531" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="533" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="628" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="630" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="636" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="638" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3305,138 +7673,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="1.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="27.7109375" style="3" customWidth="true"/>
-    <col min="3" max="3" width="12.7109375" style="4" customWidth="true"/>
-    <col min="4" max="4" width="13.4609375" style="5" customWidth="true"/>
-    <col min="5" max="5" width="10.7109375" style="6" customWidth="true"/>
-  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="50" t="s">
+    <row r="1">
+      <c r="A1" s="318" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="42" t="s">
-        <v>1</v>
-      </c>
+      <c r="B1" s="318"/>
+      <c r="C1" s="318"/>
+      <c r="D1" s="318"/>
+      <c r="E1" s="318"/>
+      <c r="F1" s="318"/>
+      <c r="G1" s="318"/>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="71" t="s">
+      <c r="A2" s="392"/>
+      <c r="B2" s="393" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="77" t="s">
-        <v>20</v>
-      </c>
+      <c r="C2" s="394"/>
+      <c r="D2" s="395"/>
+      <c r="E2" s="396" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="397"/>
+      <c r="G2" s="398"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="399" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="400" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="83">
-        <v>0.014</v>
-      </c>
-      <c r="D3" s="84" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="85">
-        <v>0.031</v>
+      <c r="C3" s="401" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="402" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="403" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="404" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="405" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="73" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="86">
-        <v>0.02</v>
-      </c>
-      <c r="D4" s="87" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="88">
-        <v>0.035000000000000003</v>
+      <c r="A4" s="406" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="407" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="408" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="409" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="410" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="411" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="412" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="74" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="89">
-        <v>-0.0060000000000000001</v>
-      </c>
-      <c r="D5" s="90" t="s">
+      <c r="A5" s="413" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="414" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="415" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="416" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="91">
-        <v>0.023</v>
+      <c r="E5" s="417" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="418" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="419" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="92">
-        <v>-0.42899999999999999</v>
-      </c>
-      <c r="D6" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="94">
-        <v>1.679</v>
+      <c r="A6" s="420" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="421" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="422" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="423" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="424" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="425" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="426" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="76" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="95">
-        <v>-0.016</v>
-      </c>
-      <c r="D7" s="96" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="97">
-        <v>0.029000000000000001</v>
-      </c>
+      <c r="A7" s="427" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="428" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="429" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="430" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="431" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="432" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="433" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="434" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="435">
+        <v>1000</v>
+      </c>
+      <c r="C8" s="436"/>
+      <c r="D8" s="437"/>
+      <c r="E8" s="438">
+        <v>1000</v>
+      </c>
+      <c r="F8" s="439"/>
+      <c r="G8" s="440"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -3446,129 +7844,267 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="99" customWidth="true"/>
-    <col min="2" max="2" width="27.7109375" style="100" customWidth="true"/>
-    <col min="3" max="3" width="12.7109375" style="101" customWidth="true"/>
-    <col min="4" max="4" width="13.4609375" style="102" customWidth="true"/>
-    <col min="5" max="5" width="10.7109375" style="103" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="125" customWidth="true"/>
+    <col min="2" max="2" width="27.7109375" style="126" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="127" customWidth="true"/>
+    <col min="4" max="4" width="13.4609375" style="128" customWidth="true"/>
+    <col min="5" max="5" width="10.7109375" style="129" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="98" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="147" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="139" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="139" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="139" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="139" t="s">
-        <v>1</v>
+    <row r="1" s="124" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="173" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="165" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="165" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="165" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="165" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="109" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="168" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="161" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="162" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="174" t="s">
-        <v>20</v>
+      <c r="A2" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="194" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="187" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="200" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="114" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="169" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="180">
+      <c r="A3" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="195" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="206">
         <v>0.014</v>
       </c>
-      <c r="D3" s="181" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="182">
+      <c r="D3" s="207" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="208">
         <v>0.031</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="119" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="170" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="183">
+      <c r="A4" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="196" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="209">
         <v>0.02</v>
       </c>
-      <c r="D4" s="184" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="185">
+      <c r="D4" s="210" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="211">
         <v>0.035000000000000003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="124" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="171" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="186">
+      <c r="A5" s="150" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="197" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="212">
         <v>-0.0060000000000000001</v>
       </c>
-      <c r="D5" s="187" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="188">
+      <c r="D5" s="213" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="214">
         <v>0.023</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="129" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="172" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="189">
+      <c r="A6" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="198" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="215">
         <v>-0.42899999999999999</v>
       </c>
-      <c r="D6" s="190" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="191">
+      <c r="D6" s="216" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="217">
         <v>1.679</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="134" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="173" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="192">
+      <c r="A7" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="199" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="218">
         <v>-0.016</v>
       </c>
-      <c r="D7" s="193" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="194">
+      <c r="D7" s="219" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="220">
+        <v>0.029000000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="222" customWidth="true"/>
+    <col min="2" max="2" width="27.7109375" style="223" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="224" customWidth="true"/>
+    <col min="4" max="4" width="13.4609375" style="225" customWidth="true"/>
+    <col min="5" max="5" width="10.7109375" style="226" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="221" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="270" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="262" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="262" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="262" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="262" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="232" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="291" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="284" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="285" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="297" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="237" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="292" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="303">
+        <v>0.014</v>
+      </c>
+      <c r="D3" s="304" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="305">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="242" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="293" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="306">
+        <v>0.02</v>
+      </c>
+      <c r="D4" s="307" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="308">
+        <v>0.035000000000000003</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="247" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="294" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="309">
+        <v>-0.0060000000000000001</v>
+      </c>
+      <c r="D5" s="310" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="311">
+        <v>0.023</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="252" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="295" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="312">
+        <v>-0.42899999999999999</v>
+      </c>
+      <c r="D6" s="313" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="314">
+        <v>1.679</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="257" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="296" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="315">
+        <v>-0.016</v>
+      </c>
+      <c r="D7" s="316" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="317">
         <v>0.029000000000000001</v>
       </c>
     </row>

--- a/gcomp/demo/demo_gcomptab.xlsx
+++ b/gcomp/demo/demo_gcomptab.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="148" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="257" uniqueCount="61">
   <si>
     <t>Table 3. Fitted component models (odds ratios)</t>
   </si>
@@ -204,10 +204,1923 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="639">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="1094">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <i/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <i/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <i/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2918,7 +4831,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="441">
+  <borders count="758">
     <border>
       <left/>
       <right/>
@@ -5934,11 +7847,2158 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="441">
+  <cellXfs count="758">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -7661,6 +11721,1238 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="638" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="441" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="442" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="443" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="444" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="445" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="446" xfId="0"/>
+    <xf numFmtId="0" fontId="640" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="642" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="644" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="646" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="648" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="650" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="652" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="654" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="656" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="658" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="660" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="662" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="664" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="666" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="668" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="670" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="672" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="674" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="676" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="678" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="680" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="682" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="684" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="686" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="688" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="690" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="692" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="694" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="696" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="698" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="700" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="702" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="704" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="706" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="708" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="710" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="712" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="714" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="716" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="718" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="719" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="720" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="721" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="723" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="725" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="727" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="729" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="731" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="732" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="733" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="734" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="735" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="736" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="737" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="738" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="739" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="740" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="741" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="742" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="743" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="744" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="745" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="746" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="747" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="748" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="749" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="750" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="751" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="752" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="753" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="754" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="755" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="756" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="757" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="758" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="759" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="760" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="761" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="762" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="763" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="764" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="765" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="767" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="769" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="771" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="773" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="538" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="539" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="540" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="541" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="542" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="543" xfId="0"/>
+    <xf numFmtId="0" fontId="776" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="778" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="780" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="782" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="784" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="786" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="788" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="790" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="792" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="794" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="796" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="802" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="804" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="806" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="808" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="810" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="814" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="816" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="818" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="820" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="822" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="824" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="826" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="828" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="830" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="832" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="834" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="836" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="838" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="840" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="842" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="844" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="846" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="848" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="850" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="852" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="854" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="855" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="856" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="857" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="859" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="861" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="863" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="865" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="867" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="868" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="869" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="870" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="871" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="872" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="873" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="874" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="875" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="876" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="877" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="878" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="879" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="880" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="881" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="882" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="883" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="884" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="885" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="886" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="887" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="888" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="889" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="890" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="891" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="892" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="893" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="894" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="895" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="896" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="897" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="898" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="899" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="900" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="901" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="902" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="903" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="904" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="905" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="906" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="907" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="908" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="909" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="910" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="912" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="914" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="915" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="917" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="918" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="919" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="920" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="921" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="923" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="924" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="926" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="927" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="929" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="930" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="932" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="933" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="934" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="935" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="936" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="938" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="939" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="941" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="942" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="947" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="949" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="951" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="953" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="955" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="957" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="959" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="961" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="963" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="965" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="967" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="969" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="971" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="973" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="975" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="977" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="979" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="981" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="983" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="985" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="987" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="989" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="991" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="993" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="995" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="997" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="999" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1001" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1003" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1005" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1007" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1009" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1011" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1013" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1015" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1031" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1035" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1047" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1049" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1051" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1053" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1055" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1057" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1059" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1061" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1063" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1065" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1067" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1069" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1071" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1073" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1075" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1077" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1079" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1081" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1083" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1085" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1087" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1089" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1091" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1093" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7677,158 +12969,158 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="318" t="s">
+      <c r="A1" s="635" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="318"/>
-      <c r="C1" s="318"/>
-      <c r="D1" s="318"/>
-      <c r="E1" s="318"/>
-      <c r="F1" s="318"/>
-      <c r="G1" s="318"/>
+      <c r="B1" s="635"/>
+      <c r="C1" s="635"/>
+      <c r="D1" s="635"/>
+      <c r="E1" s="635"/>
+      <c r="F1" s="635"/>
+      <c r="G1" s="635"/>
     </row>
     <row r="2">
-      <c r="A2" s="392"/>
-      <c r="B2" s="393" t="s">
+      <c r="A2" s="709"/>
+      <c r="B2" s="710" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="394"/>
-      <c r="D2" s="395"/>
-      <c r="E2" s="396" t="s">
+      <c r="C2" s="711"/>
+      <c r="D2" s="712"/>
+      <c r="E2" s="713" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="397"/>
-      <c r="G2" s="398"/>
+      <c r="F2" s="714"/>
+      <c r="G2" s="715"/>
     </row>
     <row r="3">
-      <c r="A3" s="399" t="s">
+      <c r="A3" s="716" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="400" t="s">
+      <c r="B3" s="717" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="401" t="s">
+      <c r="C3" s="718" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="402" t="s">
+      <c r="D3" s="719" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="403" t="s">
+      <c r="E3" s="720" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="404" t="s">
+      <c r="F3" s="721" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="405" t="s">
+      <c r="G3" s="722" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="406" t="s">
+      <c r="A4" s="723" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="407" t="s">
+      <c r="B4" s="724" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="408" t="s">
+      <c r="C4" s="725" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="409" t="s">
+      <c r="D4" s="726" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="410" t="s">
+      <c r="E4" s="727" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="411" t="s">
+      <c r="F4" s="728" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="412" t="s">
+      <c r="G4" s="729" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="413" t="s">
+      <c r="A5" s="730" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="414" t="s">
+      <c r="B5" s="731" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="415" t="s">
+      <c r="C5" s="732" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="416" t="s">
+      <c r="D5" s="733" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="417" t="s">
+      <c r="E5" s="734" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="418" t="s">
+      <c r="F5" s="735" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="419" t="s">
+      <c r="G5" s="736" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="420" t="s">
+      <c r="A6" s="737" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="421" t="s">
+      <c r="B6" s="738" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="422" t="s">
+      <c r="C6" s="739" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="423" t="s">
+      <c r="D6" s="740" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="424" t="s">
+      <c r="E6" s="741" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="425" t="s">
+      <c r="F6" s="742" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="426" t="s">
+      <c r="G6" s="743" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="427" t="s">
+      <c r="A7" s="744" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="428" t="s">
+      <c r="B7" s="745" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="429" t="s">
+      <c r="C7" s="746" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="430" t="s">
+      <c r="D7" s="747" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="431" t="s">
+      <c r="E7" s="748" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="432" t="s">
+      <c r="F7" s="749" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="433" t="s">
+      <c r="G7" s="750" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="434" t="s">
+      <c r="A8" s="751" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="435">
+      <c r="B8" s="752">
         <v>1000</v>
       </c>
-      <c r="C8" s="436"/>
-      <c r="D8" s="437"/>
-      <c r="E8" s="438">
+      <c r="C8" s="753"/>
+      <c r="D8" s="754"/>
+      <c r="E8" s="755">
         <v>1000</v>
       </c>
-      <c r="F8" s="439"/>
-      <c r="G8" s="440"/>
+      <c r="F8" s="756"/>
+      <c r="G8" s="757"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7844,129 +13136,129 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="125" customWidth="true"/>
-    <col min="2" max="2" width="27.7109375" style="126" customWidth="true"/>
-    <col min="3" max="3" width="12.7109375" style="127" customWidth="true"/>
-    <col min="4" max="4" width="13.4609375" style="128" customWidth="true"/>
-    <col min="5" max="5" width="10.7109375" style="129" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="442" customWidth="true"/>
+    <col min="2" max="2" width="27.7109375" style="443" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="444" customWidth="true"/>
+    <col min="4" max="4" width="13.4609375" style="445" customWidth="true"/>
+    <col min="5" max="5" width="10.7109375" style="446" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="124" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="173" t="s">
+    <row r="1" s="441" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="490" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="165" t="s">
+      <c r="B1" s="482" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="165" t="s">
+      <c r="C1" s="482" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="165" t="s">
+      <c r="D1" s="482" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="165" t="s">
+      <c r="E1" s="482" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="452" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="511" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C2" s="504" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="188" t="s">
+      <c r="D2" s="505" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="200" t="s">
+      <c r="E2" s="517" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="140" t="s">
+      <c r="A3" s="457" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="195" t="s">
+      <c r="B3" s="512" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="206">
+      <c r="C3" s="523">
         <v>0.014</v>
       </c>
-      <c r="D3" s="207" t="s">
+      <c r="D3" s="524" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="208">
+      <c r="E3" s="525">
         <v>0.031</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="145" t="s">
+      <c r="A4" s="462" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="196" t="s">
+      <c r="B4" s="513" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="209">
+      <c r="C4" s="526">
         <v>0.02</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="527" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="211">
+      <c r="E4" s="528">
         <v>0.035000000000000003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="467" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="197" t="s">
+      <c r="B5" s="514" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="212">
+      <c r="C5" s="529">
         <v>-0.0060000000000000001</v>
       </c>
-      <c r="D5" s="213" t="s">
+      <c r="D5" s="530" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="214">
+      <c r="E5" s="531">
         <v>0.023</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="155" t="s">
+      <c r="A6" s="472" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="198" t="s">
+      <c r="B6" s="515" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="215">
+      <c r="C6" s="532">
         <v>-0.42899999999999999</v>
       </c>
-      <c r="D6" s="216" t="s">
+      <c r="D6" s="533" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="217">
+      <c r="E6" s="534">
         <v>1.679</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="160" t="s">
+      <c r="A7" s="477" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="199" t="s">
+      <c r="B7" s="516" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="218">
+      <c r="C7" s="535">
         <v>-0.016</v>
       </c>
-      <c r="D7" s="219" t="s">
+      <c r="D7" s="536" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="220">
+      <c r="E7" s="537">
         <v>0.029000000000000001</v>
       </c>
     </row>
@@ -7982,129 +13274,129 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="222" customWidth="true"/>
-    <col min="2" max="2" width="27.7109375" style="223" customWidth="true"/>
-    <col min="3" max="3" width="12.7109375" style="224" customWidth="true"/>
-    <col min="4" max="4" width="13.4609375" style="225" customWidth="true"/>
-    <col min="5" max="5" width="10.7109375" style="226" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="539" customWidth="true"/>
+    <col min="2" max="2" width="27.7109375" style="540" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="541" customWidth="true"/>
+    <col min="4" max="4" width="13.4609375" style="542" customWidth="true"/>
+    <col min="5" max="5" width="10.7109375" style="543" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="221" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="270" t="s">
+    <row r="1" s="538" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="587" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="262" t="s">
+      <c r="B1" s="579" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="262" t="s">
+      <c r="C1" s="579" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="262" t="s">
+      <c r="D1" s="579" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="262" t="s">
+      <c r="E1" s="579" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="232" t="s">
+      <c r="A2" s="549" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="291" t="s">
+      <c r="B2" s="608" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="284" t="s">
+      <c r="C2" s="601" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="285" t="s">
+      <c r="D2" s="602" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="297" t="s">
+      <c r="E2" s="614" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="237" t="s">
+      <c r="A3" s="554" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="292" t="s">
+      <c r="B3" s="609" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="303">
+      <c r="C3" s="620">
         <v>0.014</v>
       </c>
-      <c r="D3" s="304" t="s">
+      <c r="D3" s="621" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="305">
+      <c r="E3" s="622">
         <v>0.031</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="242" t="s">
+      <c r="A4" s="559" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="293" t="s">
+      <c r="B4" s="610" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="306">
+      <c r="C4" s="623">
         <v>0.02</v>
       </c>
-      <c r="D4" s="307" t="s">
+      <c r="D4" s="624" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="308">
+      <c r="E4" s="625">
         <v>0.035000000000000003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="247" t="s">
+      <c r="A5" s="564" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="294" t="s">
+      <c r="B5" s="611" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="309">
+      <c r="C5" s="626">
         <v>-0.0060000000000000001</v>
       </c>
-      <c r="D5" s="310" t="s">
+      <c r="D5" s="627" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="311">
+      <c r="E5" s="628">
         <v>0.023</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="252" t="s">
+      <c r="A6" s="569" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="295" t="s">
+      <c r="B6" s="612" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="312">
+      <c r="C6" s="629">
         <v>-0.42899999999999999</v>
       </c>
-      <c r="D6" s="313" t="s">
+      <c r="D6" s="630" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="314">
+      <c r="E6" s="631">
         <v>1.679</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="257" t="s">
+      <c r="A7" s="574" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="296" t="s">
+      <c r="B7" s="613" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="315">
+      <c r="C7" s="632">
         <v>-0.016</v>
       </c>
-      <c r="D7" s="316" t="s">
+      <c r="D7" s="633" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="317">
+      <c r="E7" s="634">
         <v>0.029000000000000001</v>
       </c>
     </row>
